--- a/content/复原库纹样说明.xlsx
+++ b/content/复原库纹样说明.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\纹样\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ElvaSite\elva-portfolio\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="282">
   <si>
     <t>朝代</t>
   </si>
@@ -40,33 +40,7 @@
     <t>纹样名称</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3A3A42"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>纹样结构</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3A3A42"/>
-        <rFont val="var(--mono)"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF3A3A42"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>骨架</t>
-    </r>
+    <t>纹样结构/骨架</t>
   </si>
   <si>
     <t>构成元素</t>
@@ -849,13 +823,61 @@
     <t>鸳鸯纹/石榴纹/花卉纹</t>
   </si>
   <si>
-    <t>折枝卧</t>
+    <t>折枝卧鹿纹</t>
   </si>
   <si>
     <t>单独/适合/均衡</t>
   </si>
   <si>
     <t>鹿纹/十字折枝花纹/石榴纹</t>
+  </si>
+  <si>
+    <t>魏晋南北朝</t>
+  </si>
+  <si>
+    <t>双头鸟纹</t>
+  </si>
+  <si>
+    <t>鸟纹/花纹</t>
+  </si>
+  <si>
+    <t>新石器时代</t>
+  </si>
+  <si>
+    <t>旋涡纹</t>
+  </si>
+  <si>
+    <t>旋涡纹/变形鸟纹</t>
+  </si>
+  <si>
+    <t>西周</t>
+  </si>
+  <si>
+    <t>波曲纹</t>
+  </si>
+  <si>
+    <t>窃曲纹</t>
+  </si>
+  <si>
+    <t>窃曲纹/波曲纹</t>
+  </si>
+  <si>
+    <t>西魏</t>
+  </si>
+  <si>
+    <t>第285莲花忍冬藻井</t>
+  </si>
+  <si>
+    <t>忍冬纹/莲花纹/火焰纹/</t>
+  </si>
+  <si>
+    <t>现代</t>
+  </si>
+  <si>
+    <t>菱形天华锦</t>
+  </si>
+  <si>
+    <t>小团花/天华锦骨架</t>
   </si>
 </sst>
 </file>
@@ -868,7 +890,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -877,27 +899,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.75"/>
+      <sz val="9"/>
       <color rgb="FF3A3A42"/>
-      <name val="var(--mono)"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF3A3A42"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF3A3A42"/>
-      <name val="var(--mono)"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF3A3A42"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1044,14 +1060,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF3A3A42"/>
-      <name val="var(--mono)"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1061,6 +1071,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1392,163 +1408,178 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2075,17 +2106,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:D116"/>
+  <dimension ref="A3:D125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="22.75" customWidth="1"/>
     <col min="3" max="3" width="37.625" customWidth="1"/>
-    <col min="4" max="4" width="39.625" customWidth="1"/>
+    <col min="4" max="4" width="39.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" ht="21" customHeight="1" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -2094,1591 +2125,1690 @@
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1" spans="1:4">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1" spans="1:4">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1" spans="1:4">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1" spans="1:4">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1" spans="1:4">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1" spans="1:4">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1" spans="1:4">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1" spans="1:4">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1" spans="1:4">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1" spans="1:4">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1" spans="1:4">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1" spans="1:4">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1" spans="1:4">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1" spans="1:4">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1" spans="1:4">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1" spans="1:4">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1" spans="1:4">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1" spans="1:4">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1" spans="1:4">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1" spans="1:4">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1" spans="1:4">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="7" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1" spans="1:4">
-      <c r="A38" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B38" s="4" t="s">
+      <c r="A38" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1" spans="1:4">
-      <c r="A39" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B39" s="4" t="s">
+      <c r="A39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1" spans="1:4">
-      <c r="A40" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B40" s="4" t="s">
+      <c r="A40" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="7" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1" spans="1:4">
-      <c r="A41" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B41" s="4" t="s">
+      <c r="A41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="7" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1" spans="1:4">
-      <c r="A42" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B42" s="4" t="s">
+      <c r="A42" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1" spans="1:4">
-      <c r="A43" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B43" s="4" t="s">
+      <c r="A43" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="4" t="s">
+      <c r="A44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1" spans="1:4">
-      <c r="A45" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B45" s="4" t="s">
+      <c r="A45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1" spans="1:4">
-      <c r="A46" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B46" s="4" t="s">
+      <c r="A46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1" spans="1:4">
-      <c r="A47" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B47" s="8" t="s">
+      <c r="A47" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1" spans="1:4">
-      <c r="A48" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="4" t="s">
+      <c r="A48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1" spans="1:4">
-      <c r="A49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49" s="4" t="s">
+      <c r="A49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1" spans="1:4">
-      <c r="A50" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="4" t="s">
+      <c r="A50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1" spans="1:4">
-      <c r="A51" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="4" t="s">
+      <c r="A51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1" spans="1:4">
-      <c r="A52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B52" s="4" t="s">
+      <c r="A52" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1" spans="1:4">
-      <c r="A53" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B53" s="4" t="s">
+      <c r="A53" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1" spans="1:4">
-      <c r="A54" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B54" s="4" t="s">
+      <c r="A54" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1" spans="1:4">
-      <c r="A55" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B55" s="4" t="s">
+      <c r="A55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1" spans="1:4">
-      <c r="A56" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B56" s="4" t="s">
+      <c r="A56" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B57" s="4" t="s">
+      <c r="A57" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1" spans="1:4">
-      <c r="A58" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B58" s="4" t="s">
+      <c r="A58" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1" spans="1:4">
-      <c r="A59" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B59" s="4" t="s">
+      <c r="A59" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1" spans="1:4">
-      <c r="A60" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B60" s="4" t="s">
+      <c r="A60" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1" spans="1:4">
-      <c r="A61" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B61" s="4" t="s">
+      <c r="A61" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1" spans="1:4">
-      <c r="A62" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B62" s="4" t="s">
+      <c r="A62" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1" spans="1:4">
-      <c r="A63" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B63" s="4" t="s">
+      <c r="A63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1" spans="1:4">
-      <c r="A64" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B64" s="4" t="s">
+      <c r="A64" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1" spans="1:4">
-      <c r="A65" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B65" s="4" t="s">
+      <c r="A65" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1" spans="1:4">
-      <c r="A66" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B66" s="4" t="s">
+      <c r="A66" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1" spans="1:4">
-      <c r="A67" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="4" t="s">
+      <c r="A67" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1" spans="1:4">
-      <c r="A68" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B68" s="4" t="s">
+      <c r="A68" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1" spans="1:4">
-      <c r="A69" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69" s="4" t="s">
+      <c r="A69" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1" spans="1:4">
-      <c r="A70" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B70" s="4" t="s">
+      <c r="A70" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1" spans="1:4">
-      <c r="A71" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B71" s="4" t="s">
+      <c r="A71" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1" spans="1:4">
-      <c r="A72" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B72" s="4" t="s">
+      <c r="A72" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1" spans="1:4">
-      <c r="A73" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B73" s="4" t="s">
+      <c r="A73" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1" spans="1:4">
-      <c r="A74" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B74" s="4" t="s">
+      <c r="A74" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1" spans="1:4">
-      <c r="A75" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B75" s="4" t="s">
+      <c r="A75" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B75" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1" spans="1:4">
-      <c r="A76" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B76" s="4" t="s">
+      <c r="A76" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1" spans="1:4">
-      <c r="A77" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B77" s="4" t="s">
+      <c r="A77" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1" spans="1:4">
-      <c r="A78" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B78" s="4" t="s">
+      <c r="A78" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B78" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1" spans="1:4">
-      <c r="A79" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B79" s="4" t="s">
+      <c r="A79" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="7" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1" spans="1:4">
-      <c r="A80" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B80" s="4" t="s">
+      <c r="A80" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1" spans="1:4">
-      <c r="A81" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B81" s="4" t="s">
+      <c r="A81" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1" spans="1:4">
-      <c r="A82" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B82" s="4" t="s">
+      <c r="A82" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="7" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1" spans="1:4">
-      <c r="A83" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B83" s="4" t="s">
+      <c r="A83" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1" spans="1:4">
-      <c r="A84" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B84" s="4" t="s">
+      <c r="A84" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1" spans="1:4">
-      <c r="A85" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B85" s="4" t="s">
+      <c r="A85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B85" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1" spans="1:4">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1" spans="1:4">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1" spans="1:4">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1" spans="1:4">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="7" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1" spans="1:4">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="7" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1" spans="1:4">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1" spans="1:4">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1" spans="1:4">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="7" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1" spans="1:4">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" s="7" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1" spans="1:4">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="D95" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1" spans="1:4">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D96" s="7" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1" spans="1:4">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D97" s="7" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1" spans="1:4">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="7" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1" spans="1:4">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="7" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1" spans="1:4">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="7" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1" spans="1:4">
-      <c r="A101" s="3" t="s">
+      <c r="A101" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D101" s="7" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1" spans="1:4">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" s="7" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1" spans="1:4">
-      <c r="A103" s="3" t="s">
+      <c r="A103" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="D103" s="7" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1" spans="1:4">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1" spans="1:4">
-      <c r="A105" s="3" t="s">
+      <c r="A105" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D105" s="7" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1" spans="1:4">
-      <c r="A106" s="3" t="s">
+      <c r="A106" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D106" s="7" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1" spans="1:4">
-      <c r="A107" s="3" t="s">
+      <c r="A107" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D107" s="7" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1" spans="1:4">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="7" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1" spans="1:4">
-      <c r="A109" s="3" t="s">
+      <c r="A109" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="D109" s="7" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1" spans="1:4">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D110" s="7" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1" spans="1:4">
-      <c r="A111" s="3" t="s">
+      <c r="A111" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D111" s="7" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1" spans="1:4">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1" spans="1:4">
-      <c r="A113" s="3" t="s">
+      <c r="A113" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D113" s="7" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1" spans="1:4">
-      <c r="A114" s="3" t="s">
+      <c r="A114" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D114" s="7" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1" spans="1:4">
-      <c r="A115" s="3" t="s">
+      <c r="A115" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="D115" s="7" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1" spans="1:4">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D116" s="7" t="s">
         <v>265</v>
       </c>
+    </row>
+    <row r="117" ht="18" customHeight="1" spans="1:4">
+      <c r="A117" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="118" ht="14.25" spans="1:4">
+      <c r="A118" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="119" ht="14.25" spans="1:4">
+      <c r="A119" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="120" ht="14.25" spans="1:4">
+      <c r="A120" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="121" ht="14.25" spans="1:4">
+      <c r="A121" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="122" ht="14.25" spans="1:4">
+      <c r="A122" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="123" ht="16.5" spans="1:4">
+      <c r="A123" s="13"/>
+      <c r="B123" s="13"/>
+      <c r="C123" s="13"/>
+    </row>
+    <row r="124" ht="16.5" spans="1:4">
+      <c r="A124" s="13"/>
+      <c r="B124" s="13"/>
+      <c r="C124" s="13"/>
+    </row>
+    <row r="125" ht="16.5" spans="1:4">
+      <c r="A125" s="13"/>
+      <c r="B125" s="13"/>
+      <c r="C125" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
